--- a/prompt2.xlsx
+++ b/prompt2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MohitVerma\Desktop\git\translation\SaS-to-python\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFEF61A4-7E89-4CBA-B69A-4C7114C02145}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{828C32F4-8303-496A-86C3-0267C586B5AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
   </definedNames>
   <calcPr calcId="162913"/>
   <pivotCaches>
-    <pivotCache cacheId="1" r:id="rId4"/>
+    <pivotCache cacheId="4" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="496" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="273">
   <si>
     <t>Sr.No.</t>
   </si>
@@ -1146,6 +1146,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1163,18 +1175,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1207,7 +1207,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[prompt1.xlsx]NW HYSA!PivotTable2</c:name>
+    <c:name>[prompt2.xlsx]NW HYSA!PivotTable2</c:name>
     <c:fmtId val="5"/>
   </c:pivotSource>
   <c:chart>
@@ -7574,7 +7574,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7E6D0B8C-D3DB-4D61-81DB-12BC70BC81B9}" name="PivotTable2" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7E6D0B8C-D3DB-4D61-81DB-12BC70BC81B9}" name="PivotTable2" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
   <location ref="J7:AA21" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="3">
     <pivotField axis="axisRow" numFmtId="164" showAll="0">
@@ -9665,7 +9665,7 @@
       <c r="B3" s="3">
         <v>1</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="10" t="s">
         <v>48</v>
       </c>
       <c r="D3" s="2" t="s">
@@ -9679,7 +9679,7 @@
       <c r="B4" s="3">
         <v>2</v>
       </c>
-      <c r="C4" s="5"/>
+      <c r="C4" s="11"/>
       <c r="D4" s="2" t="s">
         <v>51</v>
       </c>
@@ -9691,7 +9691,7 @@
       <c r="B5" s="3">
         <v>3</v>
       </c>
-      <c r="C5" s="5"/>
+      <c r="C5" s="11"/>
       <c r="D5" s="2" t="s">
         <v>53</v>
       </c>
@@ -9703,7 +9703,7 @@
       <c r="B6" s="3">
         <v>4</v>
       </c>
-      <c r="C6" s="5"/>
+      <c r="C6" s="11"/>
       <c r="D6" s="2" t="s">
         <v>55</v>
       </c>
@@ -9715,7 +9715,7 @@
       <c r="B7" s="3">
         <v>5</v>
       </c>
-      <c r="C7" s="6"/>
+      <c r="C7" s="12"/>
       <c r="D7" s="2" t="s">
         <v>57</v>
       </c>
@@ -9727,7 +9727,7 @@
       <c r="B8" s="3">
         <v>6</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="10" t="s">
         <v>59</v>
       </c>
       <c r="D8" s="2" t="s">
@@ -9741,7 +9741,7 @@
       <c r="B9" s="3">
         <v>7</v>
       </c>
-      <c r="C9" s="5"/>
+      <c r="C9" s="11"/>
       <c r="D9" s="2" t="s">
         <v>61</v>
       </c>
@@ -9753,7 +9753,7 @@
       <c r="B10" s="3">
         <v>8</v>
       </c>
-      <c r="C10" s="5"/>
+      <c r="C10" s="11"/>
       <c r="D10" s="2" t="s">
         <v>62</v>
       </c>
@@ -9765,7 +9765,7 @@
       <c r="B11" s="2">
         <v>9</v>
       </c>
-      <c r="C11" s="5"/>
+      <c r="C11" s="11"/>
       <c r="D11" s="2" t="s">
         <v>64</v>
       </c>
@@ -9777,7 +9777,7 @@
       <c r="B12" s="2">
         <v>10</v>
       </c>
-      <c r="C12" s="6"/>
+      <c r="C12" s="12"/>
       <c r="D12" s="2" t="s">
         <v>66</v>
       </c>
@@ -9789,7 +9789,7 @@
       <c r="B13" s="2">
         <v>11</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="13" t="s">
         <v>68</v>
       </c>
       <c r="D13" s="2" t="s">
@@ -9803,7 +9803,7 @@
       <c r="B14" s="2">
         <v>12</v>
       </c>
-      <c r="C14" s="8"/>
+      <c r="C14" s="14"/>
       <c r="D14" s="2" t="s">
         <v>71</v>
       </c>
@@ -9815,7 +9815,7 @@
       <c r="B15" s="2">
         <v>13</v>
       </c>
-      <c r="C15" s="8"/>
+      <c r="C15" s="14"/>
       <c r="D15" s="2" t="s">
         <v>73</v>
       </c>
@@ -9827,7 +9827,7 @@
       <c r="B16" s="2">
         <v>14</v>
       </c>
-      <c r="C16" s="8"/>
+      <c r="C16" s="14"/>
       <c r="D16" s="2" t="s">
         <v>75</v>
       </c>
@@ -9839,7 +9839,7 @@
       <c r="B17" s="2">
         <v>15</v>
       </c>
-      <c r="C17" s="9"/>
+      <c r="C17" s="15"/>
       <c r="D17" s="2" t="s">
         <v>77</v>
       </c>
@@ -9851,7 +9851,7 @@
       <c r="B18" s="2">
         <v>16</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C18" s="13" t="s">
         <v>78</v>
       </c>
       <c r="D18" s="2" t="s">
@@ -9865,7 +9865,7 @@
       <c r="B19" s="2">
         <v>17</v>
       </c>
-      <c r="C19" s="8"/>
+      <c r="C19" s="14"/>
       <c r="D19" s="2" t="s">
         <v>81</v>
       </c>
@@ -9877,7 +9877,7 @@
       <c r="B20" s="2">
         <v>18</v>
       </c>
-      <c r="C20" s="8"/>
+      <c r="C20" s="14"/>
       <c r="D20" s="2" t="s">
         <v>83</v>
       </c>
@@ -9889,7 +9889,7 @@
       <c r="B21" s="2">
         <v>19</v>
       </c>
-      <c r="C21" s="8"/>
+      <c r="C21" s="14"/>
       <c r="D21" s="2" t="s">
         <v>85</v>
       </c>
@@ -9901,7 +9901,7 @@
       <c r="B22" s="2">
         <v>20</v>
       </c>
-      <c r="C22" s="9"/>
+      <c r="C22" s="15"/>
       <c r="D22" s="2" t="s">
         <v>87</v>
       </c>
@@ -9913,7 +9913,7 @@
       <c r="B23" s="2">
         <v>21</v>
       </c>
-      <c r="C23" s="7" t="s">
+      <c r="C23" s="13" t="s">
         <v>89</v>
       </c>
       <c r="D23" s="2" t="s">
@@ -9927,7 +9927,7 @@
       <c r="B24" s="2">
         <v>22</v>
       </c>
-      <c r="C24" s="8"/>
+      <c r="C24" s="14"/>
       <c r="D24" s="2" t="s">
         <v>92</v>
       </c>
@@ -9939,7 +9939,7 @@
       <c r="B25" s="2">
         <v>23</v>
       </c>
-      <c r="C25" s="8"/>
+      <c r="C25" s="14"/>
       <c r="D25" s="2" t="s">
         <v>94</v>
       </c>
@@ -9951,7 +9951,7 @@
       <c r="B26" s="2">
         <v>24</v>
       </c>
-      <c r="C26" s="8"/>
+      <c r="C26" s="14"/>
       <c r="D26" s="2" t="s">
         <v>96</v>
       </c>
@@ -9963,7 +9963,7 @@
       <c r="B27" s="2">
         <v>25</v>
       </c>
-      <c r="C27" s="9"/>
+      <c r="C27" s="15"/>
       <c r="D27" s="2" t="s">
         <v>98</v>
       </c>
@@ -9985,7 +9985,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD380F4D-AC9C-4F9E-8708-F19AE0363608}">
-  <dimension ref="C2:AA160"/>
+  <dimension ref="C2:AA173"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="24.26953125" bestFit="1" customWidth="1"/>
@@ -10011,26 +10011,26 @@
   </cols>
   <sheetData>
     <row r="2" spans="3:27" ht="29" x14ac:dyDescent="0.35">
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="D2" s="5" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="4" spans="3:27" x14ac:dyDescent="0.35">
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="6" t="s">
         <v>250</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="6" t="s">
         <v>251</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="6" t="s">
         <v>252</v>
       </c>
     </row>
     <row r="5" spans="3:27" x14ac:dyDescent="0.35">
-      <c r="C5" s="13">
+      <c r="C5" s="7">
         <v>45938</v>
       </c>
       <c r="D5" s="2">
@@ -10039,31 +10039,31 @@
       <c r="E5" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="G5" s="14"/>
+      <c r="G5" s="8"/>
     </row>
     <row r="6" spans="3:27" x14ac:dyDescent="0.35">
-      <c r="C6" s="13">
-        <v>45939</v>
+      <c r="C6" s="7">
+        <v>45938</v>
       </c>
       <c r="D6" s="2">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="G6" s="14"/>
+        <v>257</v>
+      </c>
+      <c r="G6" s="8"/>
     </row>
     <row r="7" spans="3:27" x14ac:dyDescent="0.35">
-      <c r="C7" s="13">
-        <v>45940</v>
+      <c r="C7" s="7">
+        <v>45938</v>
       </c>
       <c r="D7" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="G7" s="14"/>
+        <v>258</v>
+      </c>
+      <c r="G7" s="8"/>
       <c r="J7" t="s">
         <v>254</v>
       </c>
@@ -10072,16 +10072,16 @@
       </c>
     </row>
     <row r="8" spans="3:27" x14ac:dyDescent="0.35">
-      <c r="C8" s="13">
-        <v>45943</v>
+      <c r="C8" s="7">
+        <v>45938</v>
       </c>
       <c r="D8" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="G8" s="14"/>
+        <v>259</v>
+      </c>
+      <c r="G8" s="8"/>
       <c r="J8" t="s">
         <v>256</v>
       </c>
@@ -10138,17 +10138,17 @@
       </c>
     </row>
     <row r="9" spans="3:27" x14ac:dyDescent="0.35">
-      <c r="C9" s="13">
-        <v>45944</v>
+      <c r="C9" s="7">
+        <v>45938</v>
       </c>
       <c r="D9" s="2">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="G9" s="14"/>
-      <c r="J9" s="15">
+        <v>260</v>
+      </c>
+      <c r="G9" s="8"/>
+      <c r="J9" s="9">
         <v>45938</v>
       </c>
       <c r="K9">
@@ -10198,17 +10198,17 @@
       </c>
     </row>
     <row r="10" spans="3:27" x14ac:dyDescent="0.35">
-      <c r="C10" s="13">
-        <v>45945</v>
+      <c r="C10" s="7">
+        <v>45938</v>
       </c>
       <c r="D10" s="2">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="G10" s="14"/>
-      <c r="J10" s="15">
+        <v>261</v>
+      </c>
+      <c r="G10" s="8"/>
+      <c r="J10" s="9">
         <v>45939</v>
       </c>
       <c r="K10">
@@ -10258,17 +10258,17 @@
       </c>
     </row>
     <row r="11" spans="3:27" x14ac:dyDescent="0.35">
-      <c r="C11" s="13">
-        <v>45946</v>
+      <c r="C11" s="7">
+        <v>45938</v>
       </c>
       <c r="D11" s="2">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="G11" s="14"/>
-      <c r="J11" s="15">
+        <v>262</v>
+      </c>
+      <c r="G11" s="8"/>
+      <c r="J11" s="9">
         <v>45940</v>
       </c>
       <c r="K11">
@@ -10324,17 +10324,17 @@
       </c>
     </row>
     <row r="12" spans="3:27" x14ac:dyDescent="0.35">
-      <c r="C12" s="13">
-        <v>45964</v>
+      <c r="C12" s="7">
+        <v>45938</v>
       </c>
       <c r="D12" s="2">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="G12" s="14"/>
-      <c r="J12" s="15">
+        <v>263</v>
+      </c>
+      <c r="G12" s="8"/>
+      <c r="J12" s="9">
         <v>45943</v>
       </c>
       <c r="K12">
@@ -10387,17 +10387,17 @@
       </c>
     </row>
     <row r="13" spans="3:27" x14ac:dyDescent="0.35">
-      <c r="C13" s="13">
+      <c r="C13" s="7">
         <v>45938</v>
       </c>
       <c r="D13" s="2">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="G13" s="14"/>
-      <c r="J13" s="15">
+        <v>264</v>
+      </c>
+      <c r="G13" s="8"/>
+      <c r="J13" s="9">
         <v>45944</v>
       </c>
       <c r="K13">
@@ -10450,16 +10450,16 @@
       </c>
     </row>
     <row r="14" spans="3:27" x14ac:dyDescent="0.35">
-      <c r="C14" s="13">
-        <v>45939</v>
+      <c r="C14" s="7">
+        <v>45938</v>
       </c>
       <c r="D14" s="2">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="J14" s="15">
+        <v>265</v>
+      </c>
+      <c r="J14" s="9">
         <v>45945</v>
       </c>
       <c r="K14">
@@ -10512,17 +10512,17 @@
       </c>
     </row>
     <row r="15" spans="3:27" x14ac:dyDescent="0.35">
-      <c r="C15" s="13">
-        <v>45940</v>
+      <c r="C15" s="7">
+        <v>45938</v>
       </c>
       <c r="D15" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="G15" s="14"/>
-      <c r="J15" s="15">
+        <v>266</v>
+      </c>
+      <c r="G15" s="8"/>
+      <c r="J15" s="9">
         <v>45946</v>
       </c>
       <c r="K15">
@@ -10572,17 +10572,17 @@
       </c>
     </row>
     <row r="16" spans="3:27" x14ac:dyDescent="0.35">
-      <c r="C16" s="13">
-        <v>45943</v>
+      <c r="C16" s="7">
+        <v>45938</v>
       </c>
       <c r="D16" s="2">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="G16" s="14"/>
-      <c r="J16" s="15">
+        <v>267</v>
+      </c>
+      <c r="G16" s="8"/>
+      <c r="J16" s="9">
         <v>45958</v>
       </c>
       <c r="M16">
@@ -10623,17 +10623,17 @@
       </c>
     </row>
     <row r="17" spans="3:27" x14ac:dyDescent="0.35">
-      <c r="C17" s="13">
-        <v>45944</v>
+      <c r="C17" s="7">
+        <v>45938</v>
       </c>
       <c r="D17" s="2">
         <v>13</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="G17" s="14"/>
-      <c r="J17" s="15">
+        <v>268</v>
+      </c>
+      <c r="G17" s="8"/>
+      <c r="J17" s="9">
         <v>45959</v>
       </c>
       <c r="M17">
@@ -10674,17 +10674,17 @@
       </c>
     </row>
     <row r="18" spans="3:27" x14ac:dyDescent="0.35">
-      <c r="C18" s="13">
-        <v>45945</v>
+      <c r="C18" s="7">
+        <v>45938</v>
       </c>
       <c r="D18" s="2">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="G18" s="14"/>
-      <c r="J18" s="15">
+        <v>269</v>
+      </c>
+      <c r="G18" s="8"/>
+      <c r="J18" s="9">
         <v>45960</v>
       </c>
       <c r="M18">
@@ -10722,16 +10722,16 @@
       </c>
     </row>
     <row r="19" spans="3:27" x14ac:dyDescent="0.35">
-      <c r="C19" s="13">
-        <v>45946</v>
+      <c r="C19" s="7">
+        <v>45939</v>
       </c>
       <c r="D19" s="2">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="J19" s="15">
+        <v>253</v>
+      </c>
+      <c r="J19" s="9">
         <v>45961</v>
       </c>
       <c r="M19">
@@ -10769,16 +10769,16 @@
       </c>
     </row>
     <row r="20" spans="3:27" x14ac:dyDescent="0.35">
-      <c r="C20" s="13">
-        <v>45938</v>
+      <c r="C20" s="7">
+        <v>45939</v>
       </c>
       <c r="D20" s="2">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="J20" s="15">
+        <v>257</v>
+      </c>
+      <c r="J20" s="9">
         <v>45964</v>
       </c>
       <c r="K20">
@@ -10819,7 +10819,7 @@
       </c>
     </row>
     <row r="21" spans="3:27" x14ac:dyDescent="0.35">
-      <c r="C21" s="13">
+      <c r="C21" s="7">
         <v>45939</v>
       </c>
       <c r="D21" s="2">
@@ -10828,7 +10828,7 @@
       <c r="E21" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="J21" s="15" t="s">
+      <c r="J21" s="9" t="s">
         <v>272</v>
       </c>
       <c r="K21">
@@ -10884,1031 +10884,1031 @@
       </c>
     </row>
     <row r="22" spans="3:27" x14ac:dyDescent="0.35">
-      <c r="C22" s="13">
+      <c r="C22" s="7">
+        <v>45939</v>
+      </c>
+      <c r="D22" s="2">
+        <v>4</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.35">
+      <c r="C23" s="7">
+        <v>45939</v>
+      </c>
+      <c r="D23" s="2">
+        <v>3</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="24" spans="3:27" x14ac:dyDescent="0.35">
+      <c r="C24" s="7">
+        <v>45939</v>
+      </c>
+      <c r="D24" s="2">
+        <v>12</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="25" spans="3:27" x14ac:dyDescent="0.35">
+      <c r="C25" s="7">
+        <v>45939</v>
+      </c>
+      <c r="D25" s="2">
+        <v>14</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.35">
+      <c r="C26" s="7">
+        <v>45939</v>
+      </c>
+      <c r="D26" s="2">
+        <v>1</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="27" spans="3:27" x14ac:dyDescent="0.35">
+      <c r="C27" s="7">
+        <v>45939</v>
+      </c>
+      <c r="D27" s="2">
+        <v>5</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="28" spans="3:27" x14ac:dyDescent="0.35">
+      <c r="C28" s="7">
+        <v>45939</v>
+      </c>
+      <c r="D28" s="2">
+        <v>2</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.35">
+      <c r="C29" s="7">
+        <v>45939</v>
+      </c>
+      <c r="D29" s="2">
+        <v>10</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.35">
+      <c r="C30" s="7">
+        <v>45939</v>
+      </c>
+      <c r="D30" s="2">
+        <v>8</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.35">
+      <c r="C31" s="7">
+        <v>45939</v>
+      </c>
+      <c r="D31" s="2">
+        <v>13</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.35">
+      <c r="C32" s="7">
+        <v>45939</v>
+      </c>
+      <c r="D32" s="2">
+        <v>6</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="33" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C33" s="7">
         <v>45940</v>
       </c>
-      <c r="D22" s="2">
+      <c r="D33" s="2">
+        <v>8</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="34" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C34" s="7">
+        <v>45940</v>
+      </c>
+      <c r="D34" s="2">
+        <v>12</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="35" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C35" s="7">
+        <v>45940</v>
+      </c>
+      <c r="D35" s="2">
         <v>10</v>
       </c>
-      <c r="E22" s="2" t="s">
+      <c r="E35" s="2" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.35">
-      <c r="C23" s="13">
-        <v>45943</v>
-      </c>
-      <c r="D23" s="2">
-        <v>10</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.35">
-      <c r="C24" s="13">
-        <v>45944</v>
-      </c>
-      <c r="D24" s="2">
-        <v>11</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.35">
-      <c r="C25" s="13">
-        <v>45945</v>
-      </c>
-      <c r="D25" s="2">
-        <v>10</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.35">
-      <c r="C26" s="13">
-        <v>45946</v>
-      </c>
-      <c r="D26" s="2">
-        <v>10</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.35">
-      <c r="C27" s="13">
-        <v>45958</v>
-      </c>
-      <c r="D27" s="2">
-        <v>9</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.35">
-      <c r="C28" s="13">
-        <v>45959</v>
-      </c>
-      <c r="D28" s="2">
-        <v>9</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.35">
-      <c r="C29" s="13">
-        <v>45960</v>
-      </c>
-      <c r="D29" s="2">
-        <v>8</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.35">
-      <c r="C30" s="13">
-        <v>45961</v>
-      </c>
-      <c r="D30" s="2">
-        <v>7</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.35">
-      <c r="C31" s="13">
-        <v>45964</v>
-      </c>
-      <c r="D31" s="2">
-        <v>7</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.35">
-      <c r="C32" s="13">
-        <v>45938</v>
-      </c>
-      <c r="D32" s="2">
-        <v>4</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="33" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C33" s="13">
-        <v>45939</v>
-      </c>
-      <c r="D33" s="2">
-        <v>4</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="34" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C34" s="13">
+    <row r="36" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C36" s="7">
         <v>45940</v>
       </c>
-      <c r="D34" s="2">
+      <c r="D36" s="2">
         <v>5</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="35" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C35" s="13">
-        <v>45943</v>
-      </c>
-      <c r="D35" s="2">
-        <v>5</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="36" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C36" s="13">
-        <v>45944</v>
-      </c>
-      <c r="D36" s="2">
-        <v>6</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="37" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C37" s="13">
-        <v>45945</v>
+      <c r="C37" s="7">
+        <v>45940</v>
       </c>
       <c r="D37" s="2">
+        <v>4</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="38" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C38" s="7">
+        <v>45940</v>
+      </c>
+      <c r="D38" s="2">
+        <v>13</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="39" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C39" s="7">
+        <v>45940</v>
+      </c>
+      <c r="D39" s="2">
+        <v>16</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="40" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C40" s="7">
+        <v>45940</v>
+      </c>
+      <c r="D40" s="2">
+        <v>1</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="41" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C41" s="7">
+        <v>45940</v>
+      </c>
+      <c r="D41" s="2">
+        <v>3</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="42" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C42" s="7">
+        <v>45940</v>
+      </c>
+      <c r="D42" s="2">
+        <v>15</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="43" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C43" s="7">
+        <v>45940</v>
+      </c>
+      <c r="D43" s="2">
         <v>6</v>
       </c>
-      <c r="E37" s="2" t="s">
+      <c r="E43" s="3" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="44" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C44" s="7">
+        <v>45940</v>
+      </c>
+      <c r="D44" s="2">
+        <v>2</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="45" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C45" s="7">
+        <v>45940</v>
+      </c>
+      <c r="D45" s="2">
+        <v>11</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="46" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C46" s="7">
+        <v>45940</v>
+      </c>
+      <c r="D46" s="2">
+        <v>9</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="47" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C47" s="7">
+        <v>45940</v>
+      </c>
+      <c r="D47" s="2">
+        <v>14</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="48" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C48" s="7">
+        <v>45940</v>
+      </c>
+      <c r="D48" s="2">
+        <v>7</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="49" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C49" s="7">
+        <v>45943</v>
+      </c>
+      <c r="D49" s="2">
+        <v>8</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="50" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C50" s="7">
+        <v>45943</v>
+      </c>
+      <c r="D50" s="2">
+        <v>12</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="51" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C51" s="7">
+        <v>45943</v>
+      </c>
+      <c r="D51" s="2">
+        <v>10</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="52" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C52" s="7">
+        <v>45943</v>
+      </c>
+      <c r="D52" s="2">
+        <v>5</v>
+      </c>
+      <c r="E52" s="2" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="38" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C38" s="13">
-        <v>45946</v>
-      </c>
-      <c r="D38" s="2">
-        <v>6</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="39" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C39" s="13">
-        <v>45958</v>
-      </c>
-      <c r="D39" s="2">
-        <v>5</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="40" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C40" s="13">
-        <v>45959</v>
-      </c>
-      <c r="D40" s="2">
-        <v>5</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="41" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C41" s="13">
-        <v>45960</v>
-      </c>
-      <c r="D41" s="2">
+    <row r="53" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C53" s="7">
+        <v>45943</v>
+      </c>
+      <c r="D53" s="2">
         <v>4</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="42" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C42" s="13">
-        <v>45961</v>
-      </c>
-      <c r="D42" s="2">
-        <v>4</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="43" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C43" s="13">
-        <v>45964</v>
-      </c>
-      <c r="D43" s="2">
-        <v>4</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="44" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C44" s="13">
-        <v>45938</v>
-      </c>
-      <c r="D44" s="2">
-        <v>3</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="45" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C45" s="13">
-        <v>45939</v>
-      </c>
-      <c r="D45" s="2">
-        <v>3</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="46" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C46" s="13">
-        <v>45940</v>
-      </c>
-      <c r="D46" s="2">
-        <v>4</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="47" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C47" s="13">
-        <v>45943</v>
-      </c>
-      <c r="D47" s="2">
-        <v>4</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="48" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C48" s="13">
-        <v>45944</v>
-      </c>
-      <c r="D48" s="2">
-        <v>5</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="49" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C49" s="13">
-        <v>45945</v>
-      </c>
-      <c r="D49" s="2">
-        <v>3</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="50" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C50" s="13">
-        <v>45946</v>
-      </c>
-      <c r="D50" s="2">
-        <v>3</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="51" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C51" s="13">
-        <v>45958</v>
-      </c>
-      <c r="D51" s="2">
-        <v>4</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="52" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C52" s="13">
-        <v>45959</v>
-      </c>
-      <c r="D52" s="2">
-        <v>4</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="53" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C53" s="13">
-        <v>45960</v>
-      </c>
-      <c r="D53" s="2">
-        <v>3</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="54" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C54" s="13">
-        <v>45961</v>
+      <c r="C54" s="7">
+        <v>45943</v>
       </c>
       <c r="D54" s="2">
+        <v>15</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="55" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C55" s="7">
+        <v>45943</v>
+      </c>
+      <c r="D55" s="2">
+        <v>1</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="56" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C56" s="7">
+        <v>45943</v>
+      </c>
+      <c r="D56" s="2">
         <v>3</v>
       </c>
-      <c r="E54" s="2" t="s">
+      <c r="E56" s="2" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="57" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C57" s="7">
+        <v>45943</v>
+      </c>
+      <c r="D57" s="2">
+        <v>14</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="58" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C58" s="7">
+        <v>45943</v>
+      </c>
+      <c r="D58" s="2">
+        <v>6</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="59" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C59" s="7">
+        <v>45943</v>
+      </c>
+      <c r="D59" s="2">
+        <v>2</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="60" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C60" s="7">
+        <v>45943</v>
+      </c>
+      <c r="D60" s="2">
+        <v>11</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="61" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C61" s="7">
+        <v>45943</v>
+      </c>
+      <c r="D61" s="2">
+        <v>9</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="62" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C62" s="7">
+        <v>45943</v>
+      </c>
+      <c r="D62" s="2">
+        <v>13</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="63" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C63" s="7">
+        <v>45943</v>
+      </c>
+      <c r="D63" s="2">
+        <v>7</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="64" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C64" s="7">
+        <v>45944</v>
+      </c>
+      <c r="D64" s="2">
+        <v>9</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="65" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C65" s="7">
+        <v>45944</v>
+      </c>
+      <c r="D65" s="2">
+        <v>13</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="66" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C66" s="7">
+        <v>45944</v>
+      </c>
+      <c r="D66" s="2">
+        <v>11</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="67" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C67" s="7">
+        <v>45944</v>
+      </c>
+      <c r="D67" s="2">
+        <v>6</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="68" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C68" s="7">
+        <v>45944</v>
+      </c>
+      <c r="D68" s="2">
+        <v>5</v>
+      </c>
+      <c r="E68" s="2" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="55" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C55" s="13">
-        <v>45964</v>
-      </c>
-      <c r="D55" s="2">
-        <v>3</v>
-      </c>
-      <c r="E55" s="2" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="56" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C56" s="13">
-        <v>45938</v>
-      </c>
-      <c r="D56" s="2">
-        <v>12</v>
-      </c>
-      <c r="E56" s="2" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="57" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C57" s="13">
-        <v>45939</v>
-      </c>
-      <c r="D57" s="2">
-        <v>12</v>
-      </c>
-      <c r="E57" s="2" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="58" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C58" s="13">
-        <v>45940</v>
-      </c>
-      <c r="D58" s="2">
-        <v>13</v>
-      </c>
-      <c r="E58" s="2" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="59" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C59" s="13">
-        <v>45964</v>
-      </c>
-      <c r="D59" s="2">
-        <v>11</v>
-      </c>
-      <c r="E59" s="2" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="60" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C60" s="13">
-        <v>45961</v>
-      </c>
-      <c r="D60" s="2">
-        <v>10</v>
-      </c>
-      <c r="E60" s="2" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="61" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C61" s="13">
-        <v>45960</v>
-      </c>
-      <c r="D61" s="2">
-        <v>10</v>
-      </c>
-      <c r="E61" s="2" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="62" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C62" s="13">
-        <v>45959</v>
-      </c>
-      <c r="D62" s="2">
-        <v>11</v>
-      </c>
-      <c r="E62" s="2" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="63" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C63" s="13">
-        <v>45938</v>
-      </c>
-      <c r="D63" s="2">
-        <v>14</v>
-      </c>
-      <c r="E63" s="2" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="64" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C64" s="13">
-        <v>45939</v>
-      </c>
-      <c r="D64" s="2">
-        <v>14</v>
-      </c>
-      <c r="E64" s="2" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="65" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C65" s="13">
-        <v>45940</v>
-      </c>
-      <c r="D65" s="2">
-        <v>16</v>
-      </c>
-      <c r="E65" s="2" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="66" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C66" s="13">
-        <v>45943</v>
-      </c>
-      <c r="D66" s="2">
+    <row r="69" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C69" s="7">
+        <v>45944</v>
+      </c>
+      <c r="D69" s="2">
         <v>15</v>
-      </c>
-      <c r="E66" s="2" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="67" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C67" s="13">
-        <v>45944</v>
-      </c>
-      <c r="D67" s="2">
-        <v>15</v>
-      </c>
-      <c r="E67" s="2" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="68" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C68" s="13">
-        <v>45945</v>
-      </c>
-      <c r="D68" s="2">
-        <v>15</v>
-      </c>
-      <c r="E68" s="2" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="69" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C69" s="13">
-        <v>45946</v>
-      </c>
-      <c r="D69" s="2">
-        <v>14</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>262</v>
       </c>
     </row>
     <row r="70" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C70" s="13">
-        <v>45958</v>
+      <c r="C70" s="7">
+        <v>45944</v>
       </c>
       <c r="D70" s="2">
+        <v>1</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="71" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C71" s="7">
+        <v>45944</v>
+      </c>
+      <c r="D71" s="2">
+        <v>4</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="72" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C72" s="7">
+        <v>45944</v>
+      </c>
+      <c r="D72" s="2">
+        <v>3</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="73" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C73" s="7">
+        <v>45944</v>
+      </c>
+      <c r="D73" s="2">
+        <v>7</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="74" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C74" s="7">
+        <v>45944</v>
+      </c>
+      <c r="D74" s="2">
+        <v>2</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="75" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C75" s="7">
+        <v>45944</v>
+      </c>
+      <c r="D75" s="2">
+        <v>12</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="76" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C76" s="7">
+        <v>45944</v>
+      </c>
+      <c r="D76" s="2">
+        <v>10</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="77" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C77" s="7">
+        <v>45944</v>
+      </c>
+      <c r="D77" s="2">
+        <v>14</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="78" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C78" s="7">
+        <v>45944</v>
+      </c>
+      <c r="D78" s="2">
+        <v>8</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="79" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C79" s="7">
+        <v>45945</v>
+      </c>
+      <c r="D79" s="2">
+        <v>8</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="80" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C80" s="7">
+        <v>45945</v>
+      </c>
+      <c r="D80" s="2">
         <v>11</v>
       </c>
-      <c r="E70" s="2" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="71" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C71" s="13">
-        <v>45938</v>
-      </c>
-      <c r="D71" s="2">
-        <v>1</v>
-      </c>
-      <c r="E71" s="2" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="72" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C72" s="13">
-        <v>45939</v>
-      </c>
-      <c r="D72" s="2">
-        <v>1</v>
-      </c>
-      <c r="E72" s="2" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="73" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C73" s="13">
-        <v>45940</v>
-      </c>
-      <c r="D73" s="2">
-        <v>1</v>
-      </c>
-      <c r="E73" s="2" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="74" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C74" s="13">
-        <v>45943</v>
-      </c>
-      <c r="D74" s="2">
-        <v>1</v>
-      </c>
-      <c r="E74" s="2" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="75" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C75" s="13">
-        <v>45944</v>
-      </c>
-      <c r="D75" s="2">
-        <v>1</v>
-      </c>
-      <c r="E75" s="2" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="76" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C76" s="13">
+      <c r="E80" s="2" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="81" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C81" s="7">
         <v>45945</v>
       </c>
-      <c r="D76" s="2">
-        <v>1</v>
-      </c>
-      <c r="E76" s="2" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="77" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C77" s="13">
-        <v>45946</v>
-      </c>
-      <c r="D77" s="2">
-        <v>1</v>
-      </c>
-      <c r="E77" s="2" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="78" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C78" s="13">
-        <v>45940</v>
-      </c>
-      <c r="D78" s="2">
-        <v>3</v>
-      </c>
-      <c r="E78" s="2" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="79" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C79" s="13">
-        <v>45943</v>
-      </c>
-      <c r="D79" s="2">
-        <v>3</v>
-      </c>
-      <c r="E79" s="2" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="80" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C80" s="13">
-        <v>45944</v>
-      </c>
-      <c r="D80" s="2">
-        <v>4</v>
-      </c>
-      <c r="E80" s="2" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="81" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C81" s="13">
+      <c r="D81" s="2">
+        <v>10</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="82" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C82" s="7">
         <v>45945</v>
       </c>
-      <c r="D81" s="2">
-        <v>4</v>
-      </c>
-      <c r="E81" s="2" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="82" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C82" s="13">
-        <v>45946</v>
-      </c>
       <c r="D82" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>270</v>
+        <v>259</v>
       </c>
     </row>
     <row r="83" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C83" s="13">
-        <v>45958</v>
+      <c r="C83" s="7">
+        <v>45945</v>
       </c>
       <c r="D83" s="2">
         <v>3</v>
       </c>
       <c r="E83" s="2" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="84" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C84" s="7">
+        <v>45945</v>
+      </c>
+      <c r="D84" s="2">
+        <v>15</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="85" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C85" s="7">
+        <v>45945</v>
+      </c>
+      <c r="D85" s="2">
+        <v>1</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="86" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C86" s="7">
+        <v>45945</v>
+      </c>
+      <c r="D86" s="2">
+        <v>4</v>
+      </c>
+      <c r="E86" s="2" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="84" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C84" s="13">
-        <v>45959</v>
-      </c>
-      <c r="D84" s="2">
-        <v>3</v>
-      </c>
-      <c r="E84" s="2" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="85" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C85" s="13">
-        <v>45940</v>
-      </c>
-      <c r="D85" s="2">
-        <v>15</v>
-      </c>
-      <c r="E85" s="2" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="86" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C86" s="13">
-        <v>45943</v>
-      </c>
-      <c r="D86" s="2">
-        <v>14</v>
-      </c>
-      <c r="E86" s="2" t="s">
-        <v>271</v>
-      </c>
-    </row>
     <row r="87" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C87" s="13">
-        <v>45944</v>
+      <c r="C87" s="7">
+        <v>45945</v>
       </c>
       <c r="D87" s="2">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="88" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C88" s="13">
+      <c r="C88" s="7">
         <v>45945</v>
       </c>
       <c r="D88" s="2">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
     </row>
     <row r="89" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C89" s="13">
-        <v>45958</v>
+      <c r="C89" s="7">
+        <v>45945</v>
       </c>
       <c r="D89" s="2">
         <v>2</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
     </row>
     <row r="90" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C90" s="13">
-        <v>45959</v>
+      <c r="C90" s="7">
+        <v>45945</v>
       </c>
       <c r="D90" s="2">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
     </row>
     <row r="91" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C91" s="13">
-        <v>45960</v>
+      <c r="C91" s="7">
+        <v>45945</v>
       </c>
       <c r="D91" s="2">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
     </row>
     <row r="92" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C92" s="13">
-        <v>45961</v>
+      <c r="C92" s="7">
+        <v>45945</v>
       </c>
       <c r="D92" s="2">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
     </row>
     <row r="93" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C93" s="13">
-        <v>45964</v>
+      <c r="C93" s="7">
+        <v>45945</v>
       </c>
       <c r="D93" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="94" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C94" s="13">
-        <v>45964</v>
+      <c r="C94" s="7">
+        <v>45946</v>
       </c>
       <c r="D94" s="2">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>264</v>
+        <v>253</v>
       </c>
     </row>
     <row r="95" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C95" s="13">
-        <v>45938</v>
+      <c r="C95" s="7">
+        <v>45946</v>
       </c>
       <c r="D95" s="2">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
     </row>
     <row r="96" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C96" s="13">
-        <v>45939</v>
+      <c r="C96" s="7">
+        <v>45946</v>
       </c>
       <c r="D96" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
     </row>
     <row r="97" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C97" s="13">
-        <v>45940</v>
+      <c r="C97" s="7">
+        <v>45946</v>
       </c>
       <c r="D97" s="2">
         <v>6</v>
       </c>
-      <c r="E97" s="3" t="s">
-        <v>264</v>
+      <c r="E97" s="2" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="98" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C98" s="13">
-        <v>45943</v>
+      <c r="C98" s="7">
+        <v>45946</v>
       </c>
       <c r="D98" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="99" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C99" s="13">
-        <v>45944</v>
+      <c r="C99" s="7">
+        <v>45946</v>
       </c>
       <c r="D99" s="2">
+        <v>14</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="100" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C100" s="7">
+        <v>45946</v>
+      </c>
+      <c r="D100" s="2">
+        <v>1</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="101" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C101" s="7">
+        <v>45946</v>
+      </c>
+      <c r="D101" s="2">
+        <v>4</v>
+      </c>
+      <c r="E101" s="2" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="102" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C102" s="7">
+        <v>45946</v>
+      </c>
+      <c r="D102" s="2">
         <v>7</v>
-      </c>
-      <c r="E99" s="2" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="100" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C100" s="13">
-        <v>45945</v>
-      </c>
-      <c r="D100" s="2">
-        <v>7</v>
-      </c>
-      <c r="E100" s="2" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="101" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C101" s="13">
-        <v>45946</v>
-      </c>
-      <c r="D101" s="2">
-        <v>7</v>
-      </c>
-      <c r="E101" s="2" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="102" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C102" s="13">
-        <v>45958</v>
-      </c>
-      <c r="D102" s="2">
-        <v>6</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="103" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C103" s="13">
-        <v>45959</v>
+      <c r="C103" s="7">
+        <v>45946</v>
       </c>
       <c r="D103" s="2">
+        <v>2</v>
+      </c>
+      <c r="E103" s="2" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="104" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C104" s="7">
+        <v>45946</v>
+      </c>
+      <c r="D104" s="2">
+        <v>12</v>
+      </c>
+      <c r="E104" s="2" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="105" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C105" s="7">
+        <v>45946</v>
+      </c>
+      <c r="D105" s="2">
+        <v>9</v>
+      </c>
+      <c r="E105" s="2" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="106" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C106" s="7">
+        <v>45946</v>
+      </c>
+      <c r="D106" s="2">
+        <v>13</v>
+      </c>
+      <c r="E106" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="107" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C107" s="7">
+        <v>45946</v>
+      </c>
+      <c r="D107" s="2">
+        <v>5</v>
+      </c>
+      <c r="E107" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="108" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C108" s="7">
+        <v>45958</v>
+      </c>
+      <c r="D108" s="2">
+        <v>9</v>
+      </c>
+      <c r="E108" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="109" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C109" s="7">
+        <v>45958</v>
+      </c>
+      <c r="D109" s="2">
+        <v>5</v>
+      </c>
+      <c r="E109" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="110" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C110" s="7">
+        <v>45958</v>
+      </c>
+      <c r="D110" s="2">
+        <v>4</v>
+      </c>
+      <c r="E110" s="2" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="111" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C111" s="7">
+        <v>45958</v>
+      </c>
+      <c r="D111" s="2">
+        <v>11</v>
+      </c>
+      <c r="E111" s="2" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="112" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C112" s="7">
+        <v>45958</v>
+      </c>
+      <c r="D112" s="2">
+        <v>3</v>
+      </c>
+      <c r="E112" s="2" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="113" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C113" s="7">
+        <v>45958</v>
+      </c>
+      <c r="D113" s="2">
+        <v>2</v>
+      </c>
+      <c r="E113" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="114" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C114" s="7">
+        <v>45958</v>
+      </c>
+      <c r="D114" s="2">
         <v>6</v>
       </c>
-      <c r="E103" s="2" t="s">
+      <c r="E114" s="2" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="104" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C104" s="13">
-        <v>45960</v>
-      </c>
-      <c r="D104" s="2">
-        <v>5</v>
-      </c>
-      <c r="E104" s="2" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="105" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C105" s="13">
-        <v>45961</v>
-      </c>
-      <c r="D105" s="2">
-        <v>5</v>
-      </c>
-      <c r="E105" s="2" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="106" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C106" s="13">
-        <v>45938</v>
-      </c>
-      <c r="D106" s="2">
-        <v>2</v>
-      </c>
-      <c r="E106" s="2" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="107" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C107" s="13">
-        <v>45939</v>
-      </c>
-      <c r="D107" s="2">
-        <v>2</v>
-      </c>
-      <c r="E107" s="2" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="108" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C108" s="13">
-        <v>45940</v>
-      </c>
-      <c r="D108" s="2">
-        <v>2</v>
-      </c>
-      <c r="E108" s="2" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="109" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C109" s="13">
-        <v>45943</v>
-      </c>
-      <c r="D109" s="2">
-        <v>2</v>
-      </c>
-      <c r="E109" s="2" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="110" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C110" s="13">
-        <v>45944</v>
-      </c>
-      <c r="D110" s="2">
-        <v>2</v>
-      </c>
-      <c r="E110" s="2" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="111" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C111" s="13">
-        <v>45945</v>
-      </c>
-      <c r="D111" s="2">
-        <v>2</v>
-      </c>
-      <c r="E111" s="2" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="112" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C112" s="13">
-        <v>45946</v>
-      </c>
-      <c r="D112" s="2">
-        <v>2</v>
-      </c>
-      <c r="E112" s="2" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="113" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C113" s="13">
+    <row r="115" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C115" s="7">
         <v>45958</v>
-      </c>
-      <c r="D113" s="2">
-        <v>1</v>
-      </c>
-      <c r="E113" s="2" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="114" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C114" s="13">
-        <v>45959</v>
-      </c>
-      <c r="D114" s="2">
-        <v>1</v>
-      </c>
-      <c r="E114" s="2" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="115" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C115" s="13">
-        <v>45960</v>
       </c>
       <c r="D115" s="2">
         <v>1</v>
@@ -11918,504 +11918,647 @@
       </c>
     </row>
     <row r="116" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C116" s="13">
-        <v>45961</v>
+      <c r="C116" s="7">
+        <v>45958</v>
       </c>
       <c r="D116" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="117" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C117" s="13">
-        <v>45964</v>
+      <c r="C117" s="7">
+        <v>45958</v>
       </c>
       <c r="D117" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="118" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C118" s="13">
-        <v>45938</v>
+      <c r="C118" s="7">
+        <v>45958</v>
       </c>
       <c r="D118" s="2">
         <v>10</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="119" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C119" s="13">
-        <v>45939</v>
+      <c r="C119" s="7">
+        <v>45959</v>
       </c>
       <c r="D119" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
     </row>
     <row r="120" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C120" s="13">
-        <v>45940</v>
+      <c r="C120" s="7">
+        <v>45959</v>
       </c>
       <c r="D120" s="2">
+        <v>5</v>
+      </c>
+      <c r="E120" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="121" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C121" s="7">
+        <v>45959</v>
+      </c>
+      <c r="D121" s="2">
+        <v>4</v>
+      </c>
+      <c r="E121" s="2" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="122" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C122" s="7">
+        <v>45959</v>
+      </c>
+      <c r="D122" s="2">
         <v>11</v>
       </c>
-      <c r="E120" s="2" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="121" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C121" s="13">
-        <v>45943</v>
-      </c>
-      <c r="D121" s="2">
-        <v>11</v>
-      </c>
-      <c r="E121" s="2" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="122" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C122" s="13">
-        <v>45944</v>
-      </c>
-      <c r="D122" s="2">
-        <v>12</v>
-      </c>
       <c r="E122" s="2" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
     </row>
     <row r="123" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C123" s="13">
-        <v>45945</v>
+      <c r="C123" s="7">
+        <v>45959</v>
       </c>
       <c r="D123" s="2">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="124" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C124" s="13">
-        <v>45946</v>
+      <c r="C124" s="7">
+        <v>45959</v>
       </c>
       <c r="D124" s="2">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
     </row>
     <row r="125" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C125" s="13">
-        <v>45958</v>
+      <c r="C125" s="7">
+        <v>45959</v>
       </c>
       <c r="D125" s="2">
+        <v>6</v>
+      </c>
+      <c r="E125" s="2" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="126" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C126" s="7">
+        <v>45959</v>
+      </c>
+      <c r="D126" s="2">
+        <v>1</v>
+      </c>
+      <c r="E126" s="2" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="127" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C127" s="7">
+        <v>45959</v>
+      </c>
+      <c r="D127" s="2">
         <v>7</v>
-      </c>
-      <c r="E125" s="2" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="126" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C126" s="13">
-        <v>45959</v>
-      </c>
-      <c r="D126" s="2">
-        <v>7</v>
-      </c>
-      <c r="E126" s="2" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="127" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C127" s="13">
-        <v>45960</v>
-      </c>
-      <c r="D127" s="2">
-        <v>6</v>
       </c>
       <c r="E127" s="2" t="s">
         <v>266</v>
       </c>
     </row>
     <row r="128" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C128" s="13">
-        <v>45961</v>
+      <c r="C128" s="7">
+        <v>45959</v>
       </c>
       <c r="D128" s="2">
         <v>8</v>
       </c>
       <c r="E128" s="2" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="129" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C129" s="7">
+        <v>45959</v>
+      </c>
+      <c r="D129" s="2">
+        <v>10</v>
+      </c>
+      <c r="E129" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="130" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C130" s="7">
+        <v>45960</v>
+      </c>
+      <c r="D130" s="2">
+        <v>8</v>
+      </c>
+      <c r="E130" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="131" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C131" s="7">
+        <v>45960</v>
+      </c>
+      <c r="D131" s="2">
+        <v>4</v>
+      </c>
+      <c r="E131" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="132" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C132" s="7">
+        <v>45960</v>
+      </c>
+      <c r="D132" s="2">
+        <v>3</v>
+      </c>
+      <c r="E132" s="2" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="133" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C133" s="7">
+        <v>45960</v>
+      </c>
+      <c r="D133" s="2">
+        <v>10</v>
+      </c>
+      <c r="E133" s="2" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="134" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C134" s="7">
+        <v>45960</v>
+      </c>
+      <c r="D134" s="2">
+        <v>2</v>
+      </c>
+      <c r="E134" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="135" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C135" s="7">
+        <v>45960</v>
+      </c>
+      <c r="D135" s="2">
+        <v>5</v>
+      </c>
+      <c r="E135" s="2" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="136" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C136" s="7">
+        <v>45960</v>
+      </c>
+      <c r="D136" s="2">
+        <v>1</v>
+      </c>
+      <c r="E136" s="2" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="137" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C137" s="7">
+        <v>45960</v>
+      </c>
+      <c r="D137" s="2">
+        <v>6</v>
+      </c>
+      <c r="E137" s="2" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="129" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C129" s="13">
-        <v>45964</v>
-      </c>
-      <c r="D129" s="2">
-        <v>8</v>
-      </c>
-      <c r="E129" s="2" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="130" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C130" s="13">
-        <v>45964</v>
-      </c>
-      <c r="D130" s="2">
-        <v>6</v>
-      </c>
-      <c r="E130" s="2" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="131" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C131" s="13">
-        <v>45959</v>
-      </c>
-      <c r="D131" s="2">
-        <v>8</v>
-      </c>
-      <c r="E131" s="2" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="132" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C132" s="13">
-        <v>45938</v>
-      </c>
-      <c r="D132" s="2">
-        <v>8</v>
-      </c>
-      <c r="E132" s="2" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="133" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C133" s="13">
-        <v>45939</v>
-      </c>
-      <c r="D133" s="2">
-        <v>8</v>
-      </c>
-      <c r="E133" s="2" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="134" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C134" s="13">
-        <v>45940</v>
-      </c>
-      <c r="D134" s="2">
-        <v>9</v>
-      </c>
-      <c r="E134" s="2" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="135" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C135" s="13">
-        <v>45943</v>
-      </c>
-      <c r="D135" s="2">
-        <v>9</v>
-      </c>
-      <c r="E135" s="2" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="136" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C136" s="13">
-        <v>45944</v>
-      </c>
-      <c r="D136" s="2">
-        <v>10</v>
-      </c>
-      <c r="E136" s="2" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="137" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C137" s="13">
-        <v>45945</v>
-      </c>
-      <c r="D137" s="2">
-        <v>9</v>
-      </c>
-      <c r="E137" s="2" t="s">
-        <v>267</v>
-      </c>
-    </row>
     <row r="138" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C138" s="13">
-        <v>45946</v>
+      <c r="C138" s="7">
+        <v>45960</v>
       </c>
       <c r="D138" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E138" s="2" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="139" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C139" s="13">
-        <v>45958</v>
+      <c r="C139" s="7">
+        <v>45960</v>
       </c>
       <c r="D139" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="140" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C140" s="13">
-        <v>45960</v>
+      <c r="C140" s="7">
+        <v>45961</v>
       </c>
       <c r="D140" s="2">
         <v>7</v>
       </c>
       <c r="E140" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="141" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C141" s="7">
+        <v>45961</v>
+      </c>
+      <c r="D141" s="2">
+        <v>4</v>
+      </c>
+      <c r="E141" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="142" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C142" s="7">
+        <v>45961</v>
+      </c>
+      <c r="D142" s="2">
+        <v>3</v>
+      </c>
+      <c r="E142" s="2" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="143" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C143" s="7">
+        <v>45961</v>
+      </c>
+      <c r="D143" s="2">
+        <v>10</v>
+      </c>
+      <c r="E143" s="2" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="144" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C144" s="7">
+        <v>45961</v>
+      </c>
+      <c r="D144" s="2">
+        <v>2</v>
+      </c>
+      <c r="E144" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="145" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C145" s="7">
+        <v>45961</v>
+      </c>
+      <c r="D145" s="2">
+        <v>5</v>
+      </c>
+      <c r="E145" s="2" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="146" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C146" s="7">
+        <v>45961</v>
+      </c>
+      <c r="D146" s="2">
+        <v>1</v>
+      </c>
+      <c r="E146" s="2" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="147" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C147" s="7">
+        <v>45961</v>
+      </c>
+      <c r="D147" s="2">
+        <v>8</v>
+      </c>
+      <c r="E147" s="2" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="148" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C148" s="7">
+        <v>45961</v>
+      </c>
+      <c r="D148" s="2">
+        <v>6</v>
+      </c>
+      <c r="E148" s="2" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="141" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C141" s="13">
+    <row r="149" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C149" s="7">
         <v>45961</v>
       </c>
-      <c r="D141" s="2">
-        <v>6</v>
-      </c>
-      <c r="E141" s="2" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="142" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C142" s="13">
-        <v>45938</v>
-      </c>
-      <c r="D142" s="2">
-        <v>13</v>
-      </c>
-      <c r="E142" s="2" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="143" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C143" s="13">
-        <v>45939</v>
-      </c>
-      <c r="D143" s="2">
-        <v>13</v>
-      </c>
-      <c r="E143" s="2" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="144" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C144" s="13">
-        <v>45940</v>
-      </c>
-      <c r="D144" s="2">
-        <v>14</v>
-      </c>
-      <c r="E144" s="2" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="145" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C145" s="13">
-        <v>45943</v>
-      </c>
-      <c r="D145" s="2">
-        <v>13</v>
-      </c>
-      <c r="E145" s="2" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="146" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C146" s="13">
-        <v>45944</v>
-      </c>
-      <c r="D146" s="2">
-        <v>14</v>
-      </c>
-      <c r="E146" s="2" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="147" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C147" s="13">
-        <v>45945</v>
-      </c>
-      <c r="D147" s="2">
-        <v>14</v>
-      </c>
-      <c r="E147" s="2" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="148" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C148" s="13">
-        <v>45946</v>
-      </c>
-      <c r="D148" s="2">
-        <v>13</v>
-      </c>
-      <c r="E148" s="2" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="149" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C149" s="13">
-        <v>45958</v>
-      </c>
       <c r="D149" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E149" s="2" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="150" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C150" s="13">
-        <v>45959</v>
+      <c r="C150" s="7">
+        <v>45964</v>
       </c>
       <c r="D150" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>268</v>
+        <v>253</v>
       </c>
     </row>
     <row r="151" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C151" s="13">
-        <v>45960</v>
+      <c r="C151" s="7">
+        <v>45964</v>
       </c>
       <c r="D151" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E151" s="2" t="s">
-        <v>268</v>
+        <v>258</v>
       </c>
     </row>
     <row r="152" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C152" s="13">
-        <v>45961</v>
+      <c r="C152" s="7">
+        <v>45964</v>
       </c>
       <c r="D152" s="2">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E152" s="2" t="s">
-        <v>268</v>
+        <v>259</v>
       </c>
     </row>
     <row r="153" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C153" s="13">
+      <c r="C153" s="7">
         <v>45964</v>
       </c>
       <c r="D153" s="2">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E153" s="2" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
     </row>
     <row r="154" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C154" s="13">
-        <v>45938</v>
+      <c r="C154" s="7">
+        <v>45964</v>
       </c>
       <c r="D154" s="2">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
     </row>
     <row r="155" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C155" s="13">
-        <v>45939</v>
+      <c r="C155" s="7">
+        <v>45964</v>
       </c>
       <c r="D155" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E155" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="156" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C156" s="13">
-        <v>45940</v>
+      <c r="C156" s="7">
+        <v>45964</v>
       </c>
       <c r="D156" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
     </row>
     <row r="157" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C157" s="13">
-        <v>45943</v>
+      <c r="C157" s="7">
+        <v>45964</v>
       </c>
       <c r="D157" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="158" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C158" s="13">
-        <v>45944</v>
+      <c r="C158" s="7">
+        <v>45964</v>
       </c>
       <c r="D158" s="2">
         <v>8</v>
       </c>
       <c r="E158" s="2" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="159" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C159" s="13">
-        <v>45945</v>
+      <c r="C159" s="7">
+        <v>45964</v>
       </c>
       <c r="D159" s="2">
+        <v>6</v>
+      </c>
+      <c r="E159" s="2" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="160" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C160" s="7">
+        <v>45964</v>
+      </c>
+      <c r="D160" s="2">
+        <v>10</v>
+      </c>
+      <c r="E160" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="161" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C161" s="7">
+        <v>45965</v>
+      </c>
+      <c r="D161" s="2">
+        <v>8</v>
+      </c>
+      <c r="E161" s="2" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="162" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C162" s="7">
+        <v>45965</v>
+      </c>
+      <c r="D162" s="2">
+        <v>10</v>
+      </c>
+      <c r="E162" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="163" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C163" s="7">
+        <v>45965</v>
+      </c>
+      <c r="D163" s="2">
         <v>5</v>
       </c>
-      <c r="E159" s="2" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="160" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C160" s="13">
-        <v>45946</v>
-      </c>
-      <c r="D160" s="2">
-        <v>5</v>
-      </c>
-      <c r="E160" s="2" t="s">
+      <c r="E163" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="164" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C164" s="7">
+        <v>45965</v>
+      </c>
+      <c r="D164" s="2">
+        <v>4</v>
+      </c>
+      <c r="E164" s="2" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="165" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C165" s="7">
+        <v>45965</v>
+      </c>
+      <c r="D165" s="2">
+        <v>13</v>
+      </c>
+      <c r="E165" s="2" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="166" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C166" s="7">
+        <v>45965</v>
+      </c>
+      <c r="D166" s="2">
+        <v>3</v>
+      </c>
+      <c r="E166" s="2" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="167" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C167" s="7">
+        <v>45965</v>
+      </c>
+      <c r="D167" s="2">
+        <v>2</v>
+      </c>
+      <c r="E167" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="168" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C168" s="7">
+        <v>45965</v>
+      </c>
+      <c r="D168" s="2">
+        <v>6</v>
+      </c>
+      <c r="E168" s="2" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="169" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C169" s="7">
+        <v>45965</v>
+      </c>
+      <c r="D169" s="2">
+        <v>1</v>
+      </c>
+      <c r="E169" s="2" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="170" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C170" s="7">
+        <v>45965</v>
+      </c>
+      <c r="D170" s="2">
+        <v>11</v>
+      </c>
+      <c r="E170" s="2" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="171" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C171" s="7">
+        <v>45965</v>
+      </c>
+      <c r="D171" s="2">
+        <v>9</v>
+      </c>
+      <c r="E171" s="2" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="172" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C172" s="7">
+        <v>45965</v>
+      </c>
+      <c r="D172" s="2">
+        <v>12</v>
+      </c>
+      <c r="E172" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="173" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C173" s="7">
+        <v>45965</v>
+      </c>
+      <c r="D173" s="2">
+        <v>7</v>
+      </c>
+      <c r="E173" s="2" t="s">
         <v>269</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="C4:E118" xr:uid="{C13F8141-B057-41CC-9C69-E52F2BA85FD5}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C5:E160">
-      <sortCondition ref="E4:E118"/>
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C5:E173">
+      <sortCondition ref="C4:C118"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/prompt2.xlsx
+++ b/prompt2.xlsx
@@ -8,21 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MohitVerma\Desktop\git\translation\SaS-to-python\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{828C32F4-8303-496A-86C3-0267C586B5AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4F49239-3678-43AA-9E1C-FEBB18BCDD1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="prompt dictionary" sheetId="1" r:id="rId1"/>
     <sheet name="prompt best practices" sheetId="2" r:id="rId2"/>
     <sheet name="NW HYSA" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'NW HYSA'!$C$4:$E$118</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <pivotCaches>
-    <pivotCache cacheId="4" r:id="rId4"/>
+    <pivotCache cacheId="17" r:id="rId5"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="742" uniqueCount="306">
   <si>
     <t>Sr.No.</t>
   </si>
@@ -1025,6 +1026,153 @@
   <si>
     <t>Grand Total</t>
   </si>
+  <si>
+    <t>1. Extracting ranks and other Key Metrics from NW Standout Page</t>
+  </si>
+  <si>
+    <t>prompt&gt;&gt;</t>
+  </si>
+  <si>
+    <t>Visit the following page 
+https://www.nerdwallet.com/m/banking/standout-online-savings-accounts-2
+scrap all the content which is available on the page.
+extract the data under heading ```Standout Online Savings Accounts``` 
+provide the data in a tabular format 
+Rank (1, 2, 3, …)
+Bank/Institution name (short name)
+Product name (full name with bank)
+APY (annual percentage yield) (x.xx%)
+rating
+Bonus: if any (empty if not available)
+Notes: (minimum balance, eligibility, account type, restrictions — if not stated, empty)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Actual Site vs ChatGPT - </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Accuracy: 100%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">ChatGPT vs Copilot - </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Accuracy: &lt;10%</t>
+    </r>
+  </si>
+  <si>
+    <t>NW (Standout Page)</t>
+  </si>
+  <si>
+    <t>ChatGPT</t>
+  </si>
+  <si>
+    <t>Copilot</t>
+  </si>
+  <si>
+    <t>Bank/Institution name</t>
+  </si>
+  <si>
+    <t>2. Extracting ranks and other Key Metrics from NW High Yield Saving Account Page</t>
+  </si>
+  <si>
+    <t>prompt &gt;&gt;</t>
+  </si>
+  <si>
+    <t>Visit the following page 
+https://www.nerdwallet.com/best/banking/high-yield-online-savings-accounts 
+scrap all the content which is available on the page.
+extract the data under heading ```Best High-Yield Savings Accounts of {current month} 2025: ```
+provide the data in a tabular format 
+Rank (1, 2, 3, …)
+Bank/Institution name (short name)
+Product name (full name with bank)
+APY (annual percentage yield)
+rating
+Bonus: if any (empty if not available)
+Notes: (minimum balance, eligibility, account type, restrictions — if not stated, empty)</t>
+  </si>
+  <si>
+    <t>NW (HYSA page)</t>
+  </si>
+  <si>
+    <t>Varo Bank</t>
+  </si>
+  <si>
+    <t>Climate First Bank</t>
+  </si>
+  <si>
+    <t>Newtek Bank</t>
+  </si>
+  <si>
+    <t>Vio Bank</t>
+  </si>
+  <si>
+    <t>Ivy Bank</t>
+  </si>
+  <si>
+    <t>Bread Savings</t>
+  </si>
+  <si>
+    <t>Jenius Bank</t>
+  </si>
+  <si>
+    <t>Zynlo Bank</t>
+  </si>
+  <si>
+    <t>Western Alliance Bank</t>
+  </si>
+  <si>
+    <t>Bask Bank</t>
+  </si>
+  <si>
+    <t>Popular Direct</t>
+  </si>
+  <si>
+    <t>Salem Five Direct</t>
+  </si>
+  <si>
+    <t>SoFi Bank</t>
+  </si>
+  <si>
+    <t>E*TRADE</t>
+  </si>
+  <si>
+    <t>Marcus by Goldman Sachs</t>
+  </si>
+  <si>
+    <t>Western Alliance Bank (via Raisin)</t>
+  </si>
+  <si>
+    <t>Synchrony</t>
+  </si>
+  <si>
+    <t>LendingClub Bank</t>
+  </si>
+  <si>
+    <t>Openbank (Santander)</t>
+  </si>
+  <si>
+    <t>American Express Bank</t>
+  </si>
 </sst>
 </file>
 
@@ -1033,7 +1181,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1051,9 +1199,34 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1069,6 +1242,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1137,7 +1328,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1175,6 +1366,38 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6734,6 +6957,55 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>228601</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>46913</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>590551</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>174755</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F9177E7A-C471-4182-A8AE-96A513C70F43}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6299201" y="9622713"/>
+          <a:ext cx="4965700" cy="2153492"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Mohit Verma" refreshedDate="45964.706322453705" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="156" xr:uid="{1B03C5B9-65BD-4DD2-A477-9377FED367DA}">
   <cacheSource type="worksheet">
@@ -7574,7 +7846,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7E6D0B8C-D3DB-4D61-81DB-12BC70BC81B9}" name="PivotTable2" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7E6D0B8C-D3DB-4D61-81DB-12BC70BC81B9}" name="PivotTable2" cacheId="17" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
   <location ref="J7:AA21" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="3">
     <pivotField axis="axisRow" numFmtId="164" showAll="0">
@@ -12564,4 +12836,1497 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11C3316D-61E4-4165-B566-194481786465}">
+  <dimension ref="B2:J97"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="10.54296875" customWidth="1"/>
+    <col min="3" max="3" width="24.36328125" customWidth="1"/>
+    <col min="4" max="4" width="10.1796875" customWidth="1"/>
+    <col min="5" max="5" width="28" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.08984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.54296875" customWidth="1"/>
+    <col min="8" max="8" width="23.90625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.54296875" customWidth="1"/>
+    <col min="10" max="10" width="20.90625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B2" s="16">
+        <v>45966</v>
+      </c>
+    </row>
+    <row r="4" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B4" s="17" t="s">
+        <v>273</v>
+      </c>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="F4" s="19" t="s">
+        <v>274</v>
+      </c>
+      <c r="G4" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B6" s="20" t="s">
+        <v>276</v>
+      </c>
+      <c r="C6" s="20"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="20"/>
+      <c r="G6" s="20" t="s">
+        <v>277</v>
+      </c>
+      <c r="H6" s="20"/>
+      <c r="I6" s="20"/>
+      <c r="J6" s="20"/>
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B7" s="21" t="s">
+        <v>278</v>
+      </c>
+      <c r="C7" s="21"/>
+      <c r="D7" s="21" t="s">
+        <v>279</v>
+      </c>
+      <c r="E7" s="21"/>
+      <c r="G7" s="22" t="s">
+        <v>279</v>
+      </c>
+      <c r="H7" s="22"/>
+      <c r="I7" s="22" t="s">
+        <v>280</v>
+      </c>
+      <c r="J7" s="22"/>
+    </row>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B8" s="23" t="s">
+        <v>251</v>
+      </c>
+      <c r="C8" s="24" t="s">
+        <v>281</v>
+      </c>
+      <c r="D8" s="23" t="s">
+        <v>251</v>
+      </c>
+      <c r="E8" s="24" t="s">
+        <v>281</v>
+      </c>
+      <c r="F8" s="25"/>
+      <c r="G8" s="23" t="s">
+        <v>251</v>
+      </c>
+      <c r="H8" s="24" t="s">
+        <v>281</v>
+      </c>
+      <c r="I8" s="23" t="s">
+        <v>251</v>
+      </c>
+      <c r="J8" s="24" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B9" s="26">
+        <v>1</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="D9" s="26">
+        <v>1</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="G9" s="26">
+        <v>1</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="I9" s="26">
+        <v>1</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B10" s="26">
+        <v>2</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="D10" s="26">
+        <v>2</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="G10" s="26">
+        <v>2</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="I10" s="26">
+        <v>2</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B11" s="26">
+        <v>3</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="D11" s="26">
+        <v>3</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="G11" s="26">
+        <v>3</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="I11" s="26">
+        <v>3</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B12" s="26">
+        <v>4</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="D12" s="26">
+        <v>4</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="G12" s="26">
+        <v>4</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="I12" s="26">
+        <v>4</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B13" s="26">
+        <v>5</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="D13" s="26">
+        <v>5</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="G13" s="26">
+        <v>5</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="I13" s="26"/>
+      <c r="J13" s="2"/>
+    </row>
+    <row r="14" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B14" s="26">
+        <v>6</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="D14" s="26">
+        <v>6</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="G14" s="26">
+        <v>6</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="I14" s="26"/>
+      <c r="J14" s="2"/>
+    </row>
+    <row r="15" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B15" s="26">
+        <v>7</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="D15" s="26">
+        <v>7</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="G15" s="26">
+        <v>7</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="I15" s="26"/>
+      <c r="J15" s="2"/>
+    </row>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B16" s="26">
+        <v>8</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="D16" s="26">
+        <v>8</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="G16" s="26">
+        <v>8</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="I16" s="26"/>
+      <c r="J16" s="2"/>
+    </row>
+    <row r="19" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B19" s="27" t="s">
+        <v>282</v>
+      </c>
+      <c r="C19" s="28"/>
+      <c r="D19" s="28"/>
+      <c r="E19" s="29"/>
+      <c r="F19" s="19" t="s">
+        <v>283</v>
+      </c>
+      <c r="G19" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="21" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B21" s="20" t="s">
+        <v>276</v>
+      </c>
+      <c r="C21" s="20"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="20"/>
+      <c r="G21" s="20" t="s">
+        <v>277</v>
+      </c>
+      <c r="H21" s="20"/>
+      <c r="I21" s="20"/>
+      <c r="J21" s="20"/>
+    </row>
+    <row r="22" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B22" s="21" t="s">
+        <v>285</v>
+      </c>
+      <c r="C22" s="21"/>
+      <c r="D22" s="21" t="s">
+        <v>279</v>
+      </c>
+      <c r="E22" s="21"/>
+      <c r="G22" s="21" t="s">
+        <v>279</v>
+      </c>
+      <c r="H22" s="21"/>
+      <c r="I22" s="21" t="s">
+        <v>280</v>
+      </c>
+      <c r="J22" s="21"/>
+    </row>
+    <row r="23" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B23" s="24" t="s">
+        <v>251</v>
+      </c>
+      <c r="C23" s="24" t="s">
+        <v>281</v>
+      </c>
+      <c r="D23" s="24" t="s">
+        <v>251</v>
+      </c>
+      <c r="E23" s="24" t="s">
+        <v>281</v>
+      </c>
+      <c r="G23" s="24" t="s">
+        <v>251</v>
+      </c>
+      <c r="H23" s="24" t="s">
+        <v>281</v>
+      </c>
+      <c r="I23" s="24" t="s">
+        <v>251</v>
+      </c>
+      <c r="J23" s="24" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="24" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B24" s="2">
+        <v>1</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="D24" s="2">
+        <v>1</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="G24" s="2">
+        <v>1</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="I24" s="2">
+        <v>1</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="25" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B25" s="2">
+        <v>2</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="D25" s="2">
+        <v>2</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="G25" s="2">
+        <v>2</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="I25" s="2">
+        <v>2</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="26" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B26" s="2">
+        <v>3</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="D26" s="2">
+        <v>3</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="G26" s="2">
+        <v>3</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="I26" s="2">
+        <v>3</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="27" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B27" s="2">
+        <v>4</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="D27" s="2">
+        <v>4</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="G27" s="2">
+        <v>4</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="I27" s="2">
+        <v>4</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="28" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B28" s="2">
+        <v>5</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="D28" s="2">
+        <v>5</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="G28" s="2">
+        <v>5</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="I28" s="2">
+        <v>5</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="29" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B29" s="2">
+        <v>6</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="D29" s="2">
+        <v>6</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="G29" s="2">
+        <v>6</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="I29" s="2">
+        <v>6</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="30" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B30" s="2">
+        <v>7</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="D30" s="2">
+        <v>7</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="G30" s="2">
+        <v>7</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="I30" s="2">
+        <v>7</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="31" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B31" s="2">
+        <v>8</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="D31" s="2">
+        <v>8</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="G31" s="2">
+        <v>8</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="I31" s="2">
+        <v>8</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="32" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B32" s="2">
+        <v>9</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="D32" s="2">
+        <v>9</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="G32" s="2">
+        <v>9</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="I32" s="2">
+        <v>9</v>
+      </c>
+      <c r="J32" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="33" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B33" s="2">
+        <v>10</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="D33" s="2">
+        <v>10</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="G33" s="2">
+        <v>10</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="I33" s="2">
+        <v>10</v>
+      </c>
+      <c r="J33" s="2" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="34" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B34" s="2">
+        <v>11</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="D34" s="2">
+        <v>11</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="G34" s="2">
+        <v>11</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="I34" s="2">
+        <v>11</v>
+      </c>
+      <c r="J34" s="2" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="35" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B35" s="2">
+        <v>12</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="D35" s="2">
+        <v>12</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="G35" s="2">
+        <v>12</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="I35" s="2">
+        <v>12</v>
+      </c>
+      <c r="J35" s="2" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="36" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B36" s="2">
+        <v>13</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="D36" s="2">
+        <v>13</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="G36" s="2">
+        <v>13</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="I36" s="2">
+        <v>13</v>
+      </c>
+      <c r="J36" s="2" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="37" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="I37" s="2">
+        <v>14</v>
+      </c>
+      <c r="J37" s="2" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="38" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="I38" s="2">
+        <v>15</v>
+      </c>
+      <c r="J38" s="2" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="39" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="I39" s="2">
+        <v>16</v>
+      </c>
+      <c r="J39" s="2" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="40" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="I40" s="2">
+        <v>17</v>
+      </c>
+      <c r="J40" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="41" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="I41" s="2">
+        <v>18</v>
+      </c>
+      <c r="J41" s="2" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="42" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="I42" s="2">
+        <v>19</v>
+      </c>
+      <c r="J42" s="2" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="43" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="I43" s="2">
+        <v>20</v>
+      </c>
+      <c r="J43" s="2" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="44" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="I44" s="2">
+        <v>21</v>
+      </c>
+      <c r="J44" s="2" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="45" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="I45" s="2">
+        <v>22</v>
+      </c>
+      <c r="J45" s="2" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="46" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="I46" s="2">
+        <v>23</v>
+      </c>
+      <c r="J46" s="2" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="47" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="I47" s="2">
+        <v>24</v>
+      </c>
+      <c r="J47" s="2" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="48" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="I48" s="2">
+        <v>25</v>
+      </c>
+      <c r="J48" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="49" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B49" s="16">
+        <v>45968</v>
+      </c>
+    </row>
+    <row r="51" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B51" s="17" t="s">
+        <v>273</v>
+      </c>
+      <c r="C51" s="17"/>
+      <c r="D51" s="17"/>
+      <c r="F51" s="19" t="s">
+        <v>283</v>
+      </c>
+      <c r="G51" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="54" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B54" s="20" t="s">
+        <v>276</v>
+      </c>
+      <c r="C54" s="20"/>
+      <c r="D54" s="20"/>
+      <c r="E54" s="20"/>
+    </row>
+    <row r="55" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B55" s="21" t="s">
+        <v>278</v>
+      </c>
+      <c r="C55" s="21"/>
+      <c r="D55" s="21" t="s">
+        <v>279</v>
+      </c>
+      <c r="E55" s="21"/>
+    </row>
+    <row r="56" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B56" s="24" t="s">
+        <v>251</v>
+      </c>
+      <c r="C56" s="24" t="s">
+        <v>281</v>
+      </c>
+      <c r="D56" s="24" t="s">
+        <v>251</v>
+      </c>
+      <c r="E56" s="24" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="57" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B57" s="2">
+        <v>1</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="D57" s="2">
+        <v>1</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="58" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B58" s="2">
+        <v>2</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="D58" s="2">
+        <v>2</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="59" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B59" s="2">
+        <v>3</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="D59" s="2">
+        <v>3</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="60" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B60" s="2">
+        <v>4</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="D60" s="2">
+        <v>4</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="61" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B61" s="2">
+        <v>5</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="D61" s="2">
+        <v>5</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="62" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B62" s="2">
+        <v>6</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="D62" s="2">
+        <v>6</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="63" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B63" s="2">
+        <v>7</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="D63" s="2">
+        <v>7</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="64" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B64" s="2">
+        <v>8</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="D64" s="2">
+        <v>8</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="66" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B66" s="16">
+        <v>45968</v>
+      </c>
+    </row>
+    <row r="68" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B68" s="27" t="s">
+        <v>282</v>
+      </c>
+      <c r="C68" s="28"/>
+      <c r="D68" s="28"/>
+      <c r="E68" s="29"/>
+      <c r="F68" s="19" t="s">
+        <v>283</v>
+      </c>
+      <c r="G68" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="70" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B70" s="20" t="s">
+        <v>276</v>
+      </c>
+      <c r="C70" s="20"/>
+      <c r="D70" s="20"/>
+      <c r="E70" s="20"/>
+      <c r="G70" s="20" t="s">
+        <v>277</v>
+      </c>
+      <c r="H70" s="20"/>
+      <c r="I70" s="20"/>
+      <c r="J70" s="20"/>
+    </row>
+    <row r="71" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B71" s="21" t="s">
+        <v>285</v>
+      </c>
+      <c r="C71" s="21"/>
+      <c r="D71" s="21" t="s">
+        <v>279</v>
+      </c>
+      <c r="E71" s="21"/>
+      <c r="G71" s="21" t="s">
+        <v>279</v>
+      </c>
+      <c r="H71" s="21"/>
+      <c r="I71" s="21" t="s">
+        <v>280</v>
+      </c>
+      <c r="J71" s="21"/>
+    </row>
+    <row r="72" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B72" s="24" t="s">
+        <v>251</v>
+      </c>
+      <c r="C72" s="24" t="s">
+        <v>281</v>
+      </c>
+      <c r="D72" s="24" t="s">
+        <v>251</v>
+      </c>
+      <c r="E72" s="24" t="s">
+        <v>281</v>
+      </c>
+      <c r="G72" s="24" t="s">
+        <v>251</v>
+      </c>
+      <c r="H72" s="24" t="s">
+        <v>281</v>
+      </c>
+      <c r="I72" s="24" t="s">
+        <v>251</v>
+      </c>
+      <c r="J72" s="24" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="73" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B73" s="2">
+        <v>1</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="D73" s="2">
+        <v>1</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="G73" s="2">
+        <v>1</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="I73" s="2">
+        <v>1</v>
+      </c>
+      <c r="J73" s="2" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="74" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B74" s="2">
+        <v>2</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="D74" s="2">
+        <v>2</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="G74" s="2">
+        <v>2</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="I74" s="2">
+        <v>2</v>
+      </c>
+      <c r="J74" s="2" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="75" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B75" s="2">
+        <v>3</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="D75" s="2">
+        <v>3</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="G75" s="2">
+        <v>3</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="I75" s="2">
+        <v>3</v>
+      </c>
+      <c r="J75" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="76" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B76" s="2">
+        <v>4</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="D76" s="2">
+        <v>4</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="G76" s="2">
+        <v>4</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="I76" s="2">
+        <v>4</v>
+      </c>
+      <c r="J76" s="2" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="77" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B77" s="2">
+        <v>5</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="D77" s="2">
+        <v>5</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="G77" s="2">
+        <v>5</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="I77" s="2">
+        <v>5</v>
+      </c>
+      <c r="J77" s="2" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="78" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B78" s="2">
+        <v>6</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="D78" s="2">
+        <v>6</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="G78" s="2">
+        <v>6</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="I78" s="2">
+        <v>6</v>
+      </c>
+      <c r="J78" s="2" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="79" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B79" s="2">
+        <v>7</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="D79" s="2">
+        <v>7</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="G79" s="2">
+        <v>7</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="I79" s="2">
+        <v>7</v>
+      </c>
+      <c r="J79" s="2" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="80" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B80" s="2">
+        <v>8</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="D80" s="2">
+        <v>8</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="G80" s="2">
+        <v>8</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="I80" s="2">
+        <v>8</v>
+      </c>
+      <c r="J80" s="2" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="81" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B81" s="2">
+        <v>9</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="D81" s="2">
+        <v>9</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="G81" s="2">
+        <v>9</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="I81" s="2">
+        <v>9</v>
+      </c>
+      <c r="J81" s="2" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="82" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B82" s="2">
+        <v>10</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="D82" s="2">
+        <v>10</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="G82" s="2">
+        <v>10</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="I82" s="2">
+        <v>10</v>
+      </c>
+      <c r="J82" s="2" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="83" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B83" s="2">
+        <v>11</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="D83" s="2">
+        <v>11</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="G83" s="2">
+        <v>11</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="I83" s="2">
+        <v>11</v>
+      </c>
+      <c r="J83" s="2" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="84" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B84" s="2">
+        <v>12</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="D84" s="2">
+        <v>12</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="G84" s="2">
+        <v>12</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="I84" s="2">
+        <v>12</v>
+      </c>
+      <c r="J84" s="2" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="85" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B85" s="2">
+        <v>13</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="D85" s="2">
+        <v>13</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="G85" s="2">
+        <v>13</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="I85" s="2">
+        <v>13</v>
+      </c>
+      <c r="J85" s="2" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="86" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="I86" s="2">
+        <v>14</v>
+      </c>
+      <c r="J86" s="2" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="87" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="I87" s="2">
+        <v>15</v>
+      </c>
+      <c r="J87" s="2" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="88" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="I88" s="2">
+        <v>16</v>
+      </c>
+      <c r="J88" s="2" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="89" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="I89" s="2">
+        <v>17</v>
+      </c>
+      <c r="J89" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="90" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="I90" s="2">
+        <v>18</v>
+      </c>
+      <c r="J90" s="2" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="91" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="I91" s="2">
+        <v>19</v>
+      </c>
+      <c r="J91" s="2" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="92" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="I92" s="2">
+        <v>20</v>
+      </c>
+      <c r="J92" s="2" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="93" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="I93" s="2">
+        <v>21</v>
+      </c>
+      <c r="J93" s="2" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="94" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="I94" s="2">
+        <v>22</v>
+      </c>
+      <c r="J94" s="2" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="95" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="I95" s="2">
+        <v>23</v>
+      </c>
+      <c r="J95" s="2" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="96" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="I96" s="2">
+        <v>24</v>
+      </c>
+      <c r="J96" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="97" spans="9:10" x14ac:dyDescent="0.35">
+      <c r="I97" s="2">
+        <v>25</v>
+      </c>
+      <c r="J97" s="2" t="s">
+        <v>262</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="21">
+    <mergeCell ref="B54:E54"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="D55:E55"/>
+    <mergeCell ref="B70:E70"/>
+    <mergeCell ref="G70:J70"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="D71:E71"/>
+    <mergeCell ref="G71:H71"/>
+    <mergeCell ref="I71:J71"/>
+    <mergeCell ref="B21:E21"/>
+    <mergeCell ref="G21:J21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="G6:J6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="I7:J7"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>